--- a/backend_fastapi/backend_fastapi/media/excel/2_Other.xlsx
+++ b/backend_fastapi/backend_fastapi/media/excel/2_Other.xlsx
@@ -428,15 +428,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN5"/>
+  <dimension ref="A1:AN2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
@@ -449,13 +449,13 @@
     <col width="22" customWidth="1" min="16" max="16"/>
     <col width="20" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="9" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="27" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
-    <col width="19" customWidth="1" min="25" max="25"/>
+    <col width="16" customWidth="1" min="25" max="25"/>
     <col width="19" customWidth="1" min="26" max="26"/>
     <col width="29" customWidth="1" min="27" max="27"/>
     <col width="20" customWidth="1" min="28" max="28"/>
@@ -678,70 +678,72 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Smith, Schaefer and Gonzalez</t>
+          <t>Porter-Perkins</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Unit 1154 Box 8683
-DPO AE 34629</t>
+          <t>88652 James Loaf
+East Alyssamouth, KS 81684</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Smith, Schaefer and Gonzalez</t>
+          <t>Porter-Perkins</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>902-72-8574</t>
+          <t>929-76-1260</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Smith-Petersen</t>
+          <t>Castaneda LLC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>05025 Mary Fall
-Mackside, OR 70036</t>
+          <t>19558 Fry Causeway
+East Chelseytown, MD 95490</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Smith-Petersen</t>
+          <t>Castaneda LLC</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>934-70-6847</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>22083742</v>
+          <t>940-86-9734</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>46506594</t>
+        </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2014-03-01</t>
+          <t>2012-03-12</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>7200</v>
+        <v>1335.86</v>
       </c>
       <c r="S2" t="n">
-        <v>720</v>
+        <v>133.59</v>
       </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="n">
-        <v>7920</v>
+        <v>1469.45</v>
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
@@ -752,7 +754,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>10% → 720.0</t>
+          <t>10% → 133.59</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr"/>
@@ -763,14 +765,21 @@
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>IBAN:GB62IACN00896958403438</t>
+          <t>IBAN:GB49GJRS28729607733931</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>YILONG 4'x6' All over
-Handmade Carpet Dining Room
-Hand Knotted Silk Rugs 082B x2.0 @ 3600.0 = 7920.0</t>
+          <t>Nintendo 3DS Handheld Console
+Purple x5.0 @ 98.99 = 544.45 | PocketGo Bittboy v2 White
+Retro Video Game Portable
+Console - 3.5 IPS display x4.0 @ 39.0 = 171.6 | Sony PlayStation 3 Slim 120GB
+Black Console x4.0 @ 99.99 = 439.96 | Microsoft Xbox 360 - White -
+Console, Power Supply, AV
+Cables *Tested, Working* x1.0 @ 39.95 = 43.95 | SONY Playstation2 Console
+SCPH-39000 " Aqua Color " /
+TESTED 11181 x1.0 @ 45.0 = 49.5 | Nintendo 64 Console "Perfect" +
+Lot Games "6 Games" x1.0 @ 200.0 = 220.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -784,7 +793,7 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>0.948</v>
+        <v>0.871</v>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
@@ -797,326 +806,7 @@
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>Items sum (7920.0) ≈ Subtotal (7200.0). Diff: 720.00 (10.0%); Recommended field missing: Due date (due_date)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Jones, Davis and Moses</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>6622 Davis Court
-Curtismouth, MA 23635</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Jones, Davis and Moses</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Cox LLC</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>164 Dean Bypass
-Lake Stephenchester, AR 78025</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Cox LLC</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>967-86-2378</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>89299747</v>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2018-04-14</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="n">
-        <v>353.64</v>
-      </c>
-      <c r="S3" t="n">
-        <v>35.36</v>
-      </c>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="n">
-        <v>389</v>
-      </c>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>10% → 35.36</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>IBAN:GB41VOYB69288847998165</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>Vintage Crystal Red Wine
-Glasses NOS West Germany
-1983 6 10 ounce elegant stems x5.0 @ 35.45 = 194.98 | Wine Bottle Holder From Costa
-Rica Has A Parrot Painted On It x5.0 @ 5.0 = 27.5 | Birthday Girl Wine Glass by
-Lolita x2.0 @ 23.75 = 52.25 | Metal Storage Shelf Wine Glass
-Rack Wine Glasses for The
-Cabinet x2.0 @ 22.42 = 49.32 | Unicorn Wine Bottle Display x3.0 @ 15.85 = 52.3 | 100pcs Heat Shrink Capsules
-PVC Wine Bottle Caps
-Shrinkable Seal Film Covers
-3cm x2.0 @ 5.75 = 12.65</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0.946</v>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>INVOICE</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>Items sum (389.0) ≈ Subtotal (353.64). Diff: 35.36 (10.0%); Recommended field missing: Due date (due_date)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>MARJANE OUARZAZATE</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>TP:47107678</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>5201XXXXX6713</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="n">
-        <v>5.917</v>
-      </c>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>MAD</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>20.00% → 5.9167</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>(5)8410663018663
-SANDWICH CREME CHOCO = 35.5 | SURGELE @ 35.5 | ESPECES = 36.0</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0.576</v>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>INVOICE</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>Recommended field missing: Customer name (customer_name); Recommended field missing: Due date (due_date); Recommended field missing: Invoice ID (invoice_id)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>MARJANE OUARZAZATE</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>TP:47107678</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>5201XXXXX6713</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="n">
-        <v>5.917</v>
-      </c>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>MAD</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>20.00% → 5.9167</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>(5)8410663018663
-SANDWICH CREME CHOCO = 35.5 | SURGELE @ 35.5 | ESPECES = 36.0</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0.576</v>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>INVOICE</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>Recommended field missing: Customer name (customer_name); Recommended field missing: Due date (due_date); Recommended field missing: Invoice ID (invoice_id)</t>
+          <t>Items sum (1469.46) ≈ Subtotal (1335.86). Diff: 133.60 (10.0%); Recommended field missing: Due date (due_date)</t>
         </is>
       </c>
     </row>
@@ -1131,10 +821,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
@@ -1183,81 +873,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Smith, Schaefer and Gonzalez</t>
+          <t>Porter-Perkins</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>7920</v>
+        <v>1469.45</v>
       </c>
       <c r="D2" t="n">
-        <v>7920</v>
+        <v>1469.45</v>
       </c>
       <c r="E2" t="n">
-        <v>7920</v>
+        <v>1469.45</v>
       </c>
       <c r="F2" t="n">
-        <v>7920</v>
+        <v>1469.45</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>USD</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Jones, Davis and Moses</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="n">
-        <v>389</v>
-      </c>
-      <c r="D3" t="n">
-        <v>389</v>
-      </c>
-      <c r="E3" t="n">
-        <v>389</v>
-      </c>
-      <c r="F3" t="n">
-        <v>389</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>MARJANE OUARZAZATE</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" t="n">
-        <v>71</v>
-      </c>
-      <c r="D4" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="E4" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="F4" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>MAD</t>
         </is>
       </c>
     </row>
